--- a/FinalCodeBook_Upload.xlsx
+++ b/FinalCodeBook_Upload.xlsx
@@ -5700,276 +5700,276 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6453,15 +6453,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.5">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="141"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="145"/>
     </row>
     <row r="2" spans="1:7" s="57" customFormat="1" ht="28.2" x14ac:dyDescent="0.5">
       <c r="A2" s="55" t="s">
@@ -6841,15 +6841,15 @@
       <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="142" t="s">
+      <c r="A19" s="146" t="s">
         <v>334</v>
       </c>
-      <c r="B19" s="142"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="142"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
+      <c r="D19" s="146"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="146"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20" s="65" t="s">
@@ -6865,10 +6865,10 @@
       <c r="E20" s="65" t="s">
         <v>338</v>
       </c>
-      <c r="F20" s="142" t="s">
+      <c r="F20" s="146" t="s">
         <v>339</v>
       </c>
-      <c r="G20" s="142"/>
+      <c r="G20" s="146"/>
     </row>
     <row r="21" spans="1:7" ht="42.3" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="55" t="s">
@@ -6886,10 +6886,10 @@
       <c r="E21" s="66">
         <v>2026</v>
       </c>
-      <c r="F21" s="138" t="s">
+      <c r="F21" s="142" t="s">
         <v>289</v>
       </c>
-      <c r="G21" s="138"/>
+      <c r="G21" s="142"/>
     </row>
     <row r="22" spans="1:7" ht="42.3" x14ac:dyDescent="0.5">
       <c r="A22" s="55" t="s">
@@ -6907,10 +6907,10 @@
       <c r="E22" s="66">
         <v>2026</v>
       </c>
-      <c r="F22" s="138" t="s">
+      <c r="F22" s="142" t="s">
         <v>292</v>
       </c>
-      <c r="G22" s="138"/>
+      <c r="G22" s="142"/>
     </row>
     <row r="23" spans="1:7" ht="28.2" x14ac:dyDescent="0.5">
       <c r="A23" s="55" t="s">
@@ -6928,10 +6928,10 @@
       <c r="E23" s="66">
         <v>2026</v>
       </c>
-      <c r="F23" s="138" t="s">
+      <c r="F23" s="142" t="s">
         <v>294</v>
       </c>
-      <c r="G23" s="138"/>
+      <c r="G23" s="142"/>
     </row>
     <row r="24" spans="1:7" ht="42.3" x14ac:dyDescent="0.5">
       <c r="A24" s="55" t="s">
@@ -6949,10 +6949,10 @@
       <c r="E24" s="66">
         <v>2025</v>
       </c>
-      <c r="F24" s="138" t="s">
+      <c r="F24" s="142" t="s">
         <v>296</v>
       </c>
-      <c r="G24" s="138"/>
+      <c r="G24" s="142"/>
     </row>
     <row r="25" spans="1:7" ht="28.2" x14ac:dyDescent="0.5">
       <c r="A25" s="55" t="s">
@@ -6970,10 +6970,10 @@
       <c r="E25" s="66">
         <v>2026</v>
       </c>
-      <c r="F25" s="138" t="s">
+      <c r="F25" s="142" t="s">
         <v>297</v>
       </c>
-      <c r="G25" s="138"/>
+      <c r="G25" s="142"/>
     </row>
     <row r="26" spans="1:7" ht="42.3" x14ac:dyDescent="0.5">
       <c r="A26" s="55" t="s">
@@ -6991,10 +6991,10 @@
       <c r="E26" s="66">
         <v>2024</v>
       </c>
-      <c r="F26" s="138" t="s">
+      <c r="F26" s="142" t="s">
         <v>299</v>
       </c>
-      <c r="G26" s="138"/>
+      <c r="G26" s="142"/>
     </row>
     <row r="27" spans="1:7" ht="28.2" x14ac:dyDescent="0.5">
       <c r="A27" s="55" t="s">
@@ -7012,10 +7012,10 @@
       <c r="E27" s="66">
         <v>2026</v>
       </c>
-      <c r="F27" s="138" t="s">
+      <c r="F27" s="142" t="s">
         <v>301</v>
       </c>
-      <c r="G27" s="138"/>
+      <c r="G27" s="142"/>
     </row>
     <row r="28" spans="1:7" ht="28.2" x14ac:dyDescent="0.5">
       <c r="A28" s="55" t="s">
@@ -7033,10 +7033,10 @@
       <c r="E28" s="67">
         <v>2026</v>
       </c>
-      <c r="F28" s="137" t="s">
+      <c r="F28" s="141" t="s">
         <v>304</v>
       </c>
-      <c r="G28" s="137"/>
+      <c r="G28" s="141"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -7087,18 +7087,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="145"/>
+      <c r="B2" s="148"/>
+      <c r="C2" s="149"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11" t="s">
@@ -7178,11 +7178,11 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="143" t="s">
+      <c r="A12" s="147" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="144"/>
-      <c r="C12" s="145"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="149"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11" t="s">
@@ -7306,18 +7306,18 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="146" t="s">
+      <c r="A25" s="150" t="s">
         <v>183</v>
       </c>
-      <c r="B25" s="146"/>
-      <c r="C25" s="146"/>
+      <c r="B25" s="150"/>
+      <c r="C25" s="150"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="143" t="s">
+      <c r="A26" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="144"/>
-      <c r="C26" s="145"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="149"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11" t="s">
@@ -7386,11 +7386,11 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="143" t="s">
+      <c r="A34" s="147" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="144"/>
-      <c r="C34" s="145"/>
+      <c r="B34" s="148"/>
+      <c r="C34" s="149"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11" t="s">
@@ -7487,11 +7487,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="159" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
     </row>
     <row r="2" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="43" t="s">
@@ -7541,13 +7541,13 @@
       <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="152" t="s">
         <v>255</v>
       </c>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="44" t="s">
@@ -7565,13 +7565,13 @@
       <c r="E8" s="155"/>
     </row>
     <row r="9" spans="1:5" s="10" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="152" t="s">
+      <c r="A9" s="157" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="147" t="s">
+      <c r="B9" s="158" t="s">
         <v>257</v>
       </c>
-      <c r="C9" s="147" t="s">
+      <c r="C9" s="158" t="s">
         <v>188</v>
       </c>
       <c r="D9" s="154" t="s">
@@ -7580,13 +7580,13 @@
       <c r="E9" s="154"/>
     </row>
     <row r="10" spans="1:5" s="10" customFormat="1" ht="57.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="152"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="147"/>
-      <c r="D10" s="148" t="s">
+      <c r="A10" s="157"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="151" t="s">
         <v>189</v>
       </c>
-      <c r="E10" s="148"/>
+      <c r="E10" s="151"/>
     </row>
     <row r="11" spans="1:5" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="44" t="s">
@@ -7598,43 +7598,43 @@
       <c r="C11" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="D11" s="148" t="s">
+      <c r="D11" s="151" t="s">
         <v>264</v>
       </c>
-      <c r="E11" s="148"/>
+      <c r="E11" s="151"/>
     </row>
     <row r="12" spans="1:5" ht="33.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="148" t="s">
+      <c r="B12" s="151" t="s">
         <v>259</v>
       </c>
-      <c r="C12" s="148"/>
-      <c r="D12" s="148"/>
-      <c r="E12" s="148"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
     </row>
     <row r="13" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="152" t="s">
+      <c r="A13" s="157" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="147" t="s">
+      <c r="B13" s="158" t="s">
         <v>260</v>
       </c>
-      <c r="C13" s="147" t="s">
+      <c r="C13" s="158" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="148" t="s">
+      <c r="D13" s="151" t="s">
         <v>281</v>
       </c>
-      <c r="E13" s="148"/>
+      <c r="E13" s="151"/>
     </row>
     <row r="14" spans="1:5" ht="86.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="152"/>
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
+      <c r="A14" s="157"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
     </row>
     <row r="15" spans="1:5" ht="62.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="44" t="s">
@@ -7646,18 +7646,18 @@
       <c r="C15" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="D15" s="148" t="s">
+      <c r="D15" s="151" t="s">
         <v>282</v>
       </c>
-      <c r="E15" s="148"/>
+      <c r="E15" s="151"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="146" t="s">
+      <c r="A17" s="150" t="s">
         <v>265</v>
       </c>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="146"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="150"/>
     </row>
     <row r="18" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="9" t="s">
@@ -7684,21 +7684,21 @@
       <c r="D20" s="15"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="146" t="s">
+      <c r="A22" s="150" t="s">
         <v>266</v>
       </c>
-      <c r="B22" s="146"/>
-      <c r="C22" s="146"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="151" t="s">
+      <c r="B23" s="152" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="151"/>
-      <c r="D23" s="151"/>
-      <c r="E23" s="151"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="49" t="s">
@@ -7824,12 +7824,12 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="151" t="s">
+      <c r="B32" s="152" t="s">
         <v>183</v>
       </c>
-      <c r="C32" s="151"/>
-      <c r="D32" s="151"/>
-      <c r="E32" s="151"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -7973,6 +7973,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="B23:E23"/>
@@ -7989,15 +7998,6 @@
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8023,56 +8023,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="163"/>
-      <c r="G1" s="163"/>
-      <c r="H1" s="163"/>
-      <c r="I1" s="163"/>
-      <c r="J1" s="163"/>
-      <c r="K1" s="163"/>
-      <c r="L1" s="163"/>
-      <c r="M1" s="163"/>
-      <c r="N1" s="163"/>
-      <c r="O1" s="163"/>
-      <c r="P1" s="164"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="162"/>
+      <c r="G1" s="162"/>
+      <c r="H1" s="162"/>
+      <c r="I1" s="162"/>
+      <c r="J1" s="162"/>
+      <c r="K1" s="162"/>
+      <c r="L1" s="162"/>
+      <c r="M1" s="162"/>
+      <c r="N1" s="162"/>
+      <c r="O1" s="162"/>
+      <c r="P1" s="163"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="157" t="s">
+      <c r="B2" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="158" t="s">
+      <c r="C2" s="165" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="161" t="s">
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
+      <c r="G2" s="166"/>
+      <c r="H2" s="166"/>
+      <c r="I2" s="166"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="166"/>
+      <c r="L2" s="166"/>
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="P2" s="161" t="s">
+      <c r="P2" s="168" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A3" s="157"/>
-      <c r="B3" s="157"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
       <c r="C3" s="16" t="s">
         <v>65</v>
       </c>
@@ -8109,8 +8109,8 @@
       <c r="N3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="O3" s="161"/>
-      <c r="P3" s="161"/>
+      <c r="O3" s="168"/>
+      <c r="P3" s="168"/>
       <c r="R3" s="16" t="s">
         <v>77</v>
       </c>
@@ -9030,24 +9030,24 @@
       </c>
     </row>
     <row r="20" spans="1:24" ht="25.2" x14ac:dyDescent="0.45">
-      <c r="A20" s="162" t="s">
+      <c r="A20" s="161" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="163"/>
-      <c r="C20" s="163"/>
-      <c r="D20" s="163"/>
-      <c r="E20" s="163"/>
-      <c r="F20" s="163"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="163"/>
-      <c r="I20" s="163"/>
-      <c r="J20" s="163"/>
-      <c r="K20" s="163"/>
-      <c r="L20" s="163"/>
-      <c r="M20" s="163"/>
-      <c r="N20" s="163"/>
-      <c r="O20" s="163"/>
-      <c r="P20" s="164"/>
+      <c r="B20" s="162"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="162"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="162"/>
+      <c r="K20" s="162"/>
+      <c r="L20" s="162"/>
+      <c r="M20" s="162"/>
+      <c r="N20" s="162"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
       <c r="S20" s="21" t="s">
         <v>121</v>
       </c>
@@ -9056,37 +9056,37 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.45">
-      <c r="A21" s="157" t="s">
+      <c r="A21" s="164" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="157" t="s">
+      <c r="B21" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="158" t="s">
+      <c r="C21" s="165" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="159"/>
-      <c r="K21" s="159"/>
-      <c r="L21" s="159"/>
-      <c r="M21" s="159"/>
-      <c r="N21" s="160"/>
-      <c r="O21" s="161" t="s">
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="166"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="166"/>
+      <c r="N21" s="167"/>
+      <c r="O21" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="161" t="s">
+      <c r="P21" s="168" t="s">
         <v>124</v>
       </c>
       <c r="T21" s="26"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.45">
-      <c r="A22" s="157"/>
-      <c r="B22" s="157"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="164"/>
       <c r="C22" s="16" t="s">
         <v>65</v>
       </c>
@@ -9123,8 +9123,8 @@
       <c r="N22" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="O22" s="161"/>
-      <c r="P22" s="161"/>
+      <c r="O22" s="168"/>
+      <c r="P22" s="168"/>
       <c r="T22" s="22"/>
     </row>
     <row r="23" spans="1:24" ht="25.2" x14ac:dyDescent="0.45">
@@ -9799,6 +9799,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:N21"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="P21:P22"/>
     <mergeCell ref="A20:P20"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:A3"/>
@@ -9806,11 +9811,6 @@
     <mergeCell ref="C2:N2"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:N21"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="P21:P22"/>
   </mergeCells>
   <conditionalFormatting sqref="A10:A11">
     <cfRule type="duplicateValues" dxfId="10" priority="1"/>
@@ -9873,208 +9873,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="171" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
-      <c r="J1" s="181"/>
-      <c r="K1" s="181"/>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
-      <c r="N1" s="181"/>
-      <c r="O1" s="181"/>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="181"/>
-      <c r="T1" s="181"/>
-      <c r="U1" s="181"/>
-      <c r="V1" s="181"/>
-      <c r="W1" s="181"/>
-      <c r="X1" s="181"/>
-      <c r="Y1" s="181"/>
-      <c r="Z1" s="181"/>
-      <c r="AA1" s="181"/>
-      <c r="AB1" s="181"/>
-      <c r="AC1" s="181"/>
-      <c r="AD1" s="181"/>
-      <c r="AE1" s="181"/>
-      <c r="AF1" s="181"/>
-      <c r="AG1" s="181"/>
-      <c r="AH1" s="181"/>
-      <c r="AI1" s="181"/>
-      <c r="AJ1" s="181"/>
-      <c r="AK1" s="181"/>
-      <c r="AL1" s="181"/>
-      <c r="AM1" s="181"/>
-      <c r="AN1" s="181"/>
-      <c r="AO1" s="181"/>
-      <c r="AP1" s="181"/>
-      <c r="AQ1" s="181"/>
-      <c r="AR1" s="181"/>
-      <c r="AS1" s="181"/>
-      <c r="AT1" s="181"/>
-      <c r="AU1" s="181"/>
-      <c r="AV1" s="181"/>
-      <c r="AW1" s="181"/>
-      <c r="AX1" s="181"/>
-      <c r="AY1" s="181"/>
-      <c r="AZ1" s="181"/>
-      <c r="BA1" s="181"/>
-      <c r="BB1" s="181"/>
-      <c r="BC1" s="181"/>
-      <c r="BD1" s="181"/>
-      <c r="BE1" s="181"/>
-      <c r="BF1" s="181"/>
-      <c r="BG1" s="181"/>
-      <c r="BH1" s="181"/>
-      <c r="BI1" s="181"/>
-      <c r="BJ1" s="181"/>
-      <c r="BK1" s="181"/>
-      <c r="BL1" s="181"/>
-      <c r="BM1" s="181"/>
-      <c r="BN1" s="181"/>
-      <c r="BO1" s="181"/>
-      <c r="BP1" s="181"/>
-      <c r="BQ1" s="181"/>
-      <c r="BR1" s="181"/>
-      <c r="BS1" s="182"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
+      <c r="G1" s="172"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="172"/>
+      <c r="K1" s="172"/>
+      <c r="L1" s="172"/>
+      <c r="M1" s="172"/>
+      <c r="N1" s="172"/>
+      <c r="O1" s="172"/>
+      <c r="P1" s="172"/>
+      <c r="Q1" s="172"/>
+      <c r="R1" s="172"/>
+      <c r="S1" s="172"/>
+      <c r="T1" s="172"/>
+      <c r="U1" s="172"/>
+      <c r="V1" s="172"/>
+      <c r="W1" s="172"/>
+      <c r="X1" s="172"/>
+      <c r="Y1" s="172"/>
+      <c r="Z1" s="172"/>
+      <c r="AA1" s="172"/>
+      <c r="AB1" s="172"/>
+      <c r="AC1" s="172"/>
+      <c r="AD1" s="172"/>
+      <c r="AE1" s="172"/>
+      <c r="AF1" s="172"/>
+      <c r="AG1" s="172"/>
+      <c r="AH1" s="172"/>
+      <c r="AI1" s="172"/>
+      <c r="AJ1" s="172"/>
+      <c r="AK1" s="172"/>
+      <c r="AL1" s="172"/>
+      <c r="AM1" s="172"/>
+      <c r="AN1" s="172"/>
+      <c r="AO1" s="172"/>
+      <c r="AP1" s="172"/>
+      <c r="AQ1" s="172"/>
+      <c r="AR1" s="172"/>
+      <c r="AS1" s="172"/>
+      <c r="AT1" s="172"/>
+      <c r="AU1" s="172"/>
+      <c r="AV1" s="172"/>
+      <c r="AW1" s="172"/>
+      <c r="AX1" s="172"/>
+      <c r="AY1" s="172"/>
+      <c r="AZ1" s="172"/>
+      <c r="BA1" s="172"/>
+      <c r="BB1" s="172"/>
+      <c r="BC1" s="172"/>
+      <c r="BD1" s="172"/>
+      <c r="BE1" s="172"/>
+      <c r="BF1" s="172"/>
+      <c r="BG1" s="172"/>
+      <c r="BH1" s="172"/>
+      <c r="BI1" s="172"/>
+      <c r="BJ1" s="172"/>
+      <c r="BK1" s="172"/>
+      <c r="BL1" s="172"/>
+      <c r="BM1" s="172"/>
+      <c r="BN1" s="172"/>
+      <c r="BO1" s="172"/>
+      <c r="BP1" s="172"/>
+      <c r="BQ1" s="172"/>
+      <c r="BR1" s="172"/>
+      <c r="BS1" s="173"/>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="120"/>
       <c r="B2" s="120"/>
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="192" t="s">
         <v>362</v>
       </c>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="166"/>
-      <c r="G2" s="166"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="166"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="166"/>
-      <c r="M2" s="166"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="166"/>
-      <c r="P2" s="167"/>
-      <c r="Q2" s="183" t="s">
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="180"/>
+      <c r="K2" s="180"/>
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="180"/>
+      <c r="O2" s="180"/>
+      <c r="P2" s="181"/>
+      <c r="Q2" s="182" t="s">
         <v>442</v>
       </c>
-      <c r="R2" s="185"/>
-      <c r="S2" s="185"/>
-      <c r="T2" s="185"/>
-      <c r="U2" s="185"/>
-      <c r="V2" s="185"/>
-      <c r="W2" s="185"/>
-      <c r="X2" s="185"/>
-      <c r="Y2" s="185"/>
-      <c r="Z2" s="185"/>
-      <c r="AA2" s="185"/>
-      <c r="AB2" s="185"/>
-      <c r="AC2" s="185"/>
-      <c r="AD2" s="185"/>
-      <c r="AE2" s="185"/>
-      <c r="AF2" s="185"/>
-      <c r="AG2" s="185"/>
-      <c r="AH2" s="185"/>
-      <c r="AI2" s="178"/>
-      <c r="AJ2" s="178"/>
-      <c r="AK2" s="178"/>
-      <c r="AL2" s="178"/>
-      <c r="AM2" s="178"/>
-      <c r="AN2" s="178"/>
-      <c r="AO2" s="178"/>
-      <c r="AP2" s="178"/>
-      <c r="AQ2" s="178"/>
-      <c r="AR2" s="178"/>
-      <c r="AS2" s="178"/>
-      <c r="AT2" s="178"/>
-      <c r="AU2" s="178"/>
-      <c r="AV2" s="178"/>
-      <c r="AW2" s="178"/>
-      <c r="AX2" s="178"/>
-      <c r="AY2" s="178"/>
-      <c r="AZ2" s="178"/>
-      <c r="BA2" s="178"/>
-      <c r="BB2" s="178"/>
-      <c r="BC2" s="178"/>
-      <c r="BD2" s="178"/>
-      <c r="BE2" s="178"/>
-      <c r="BF2" s="179"/>
-      <c r="BG2" s="179"/>
-      <c r="BH2" s="179"/>
-      <c r="BI2" s="179"/>
-      <c r="BJ2" s="179"/>
-      <c r="BK2" s="179"/>
-      <c r="BL2" s="179"/>
-      <c r="BM2" s="179"/>
-      <c r="BN2" s="179"/>
-      <c r="BO2" s="179"/>
-      <c r="BP2" s="179"/>
-      <c r="BQ2" s="179"/>
-      <c r="BR2" s="179"/>
-      <c r="BS2" s="179"/>
+      <c r="R2" s="184"/>
+      <c r="S2" s="184"/>
+      <c r="T2" s="184"/>
+      <c r="U2" s="184"/>
+      <c r="V2" s="184"/>
+      <c r="W2" s="184"/>
+      <c r="X2" s="184"/>
+      <c r="Y2" s="184"/>
+      <c r="Z2" s="184"/>
+      <c r="AA2" s="184"/>
+      <c r="AB2" s="184"/>
+      <c r="AC2" s="184"/>
+      <c r="AD2" s="184"/>
+      <c r="AE2" s="184"/>
+      <c r="AF2" s="184"/>
+      <c r="AG2" s="184"/>
+      <c r="AH2" s="184"/>
+      <c r="AI2" s="190"/>
+      <c r="AJ2" s="190"/>
+      <c r="AK2" s="190"/>
+      <c r="AL2" s="190"/>
+      <c r="AM2" s="190"/>
+      <c r="AN2" s="190"/>
+      <c r="AO2" s="190"/>
+      <c r="AP2" s="190"/>
+      <c r="AQ2" s="190"/>
+      <c r="AR2" s="190"/>
+      <c r="AS2" s="190"/>
+      <c r="AT2" s="190"/>
+      <c r="AU2" s="190"/>
+      <c r="AV2" s="190"/>
+      <c r="AW2" s="190"/>
+      <c r="AX2" s="190"/>
+      <c r="AY2" s="190"/>
+      <c r="AZ2" s="190"/>
+      <c r="BA2" s="190"/>
+      <c r="BB2" s="190"/>
+      <c r="BC2" s="190"/>
+      <c r="BD2" s="190"/>
+      <c r="BE2" s="190"/>
+      <c r="BF2" s="191"/>
+      <c r="BG2" s="191"/>
+      <c r="BH2" s="191"/>
+      <c r="BI2" s="191"/>
+      <c r="BJ2" s="191"/>
+      <c r="BK2" s="191"/>
+      <c r="BL2" s="191"/>
+      <c r="BM2" s="191"/>
+      <c r="BN2" s="191"/>
+      <c r="BO2" s="191"/>
+      <c r="BP2" s="191"/>
+      <c r="BQ2" s="191"/>
+      <c r="BR2" s="191"/>
+      <c r="BS2" s="191"/>
     </row>
     <row r="3" spans="1:71" ht="25.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="120"/>
       <c r="B3" s="120"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="193" t="s">
         <v>363</v>
       </c>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
-      <c r="L3" s="166" t="s">
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
+      <c r="L3" s="180" t="s">
         <v>364</v>
       </c>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="167"/>
+      <c r="M3" s="180"/>
+      <c r="N3" s="180"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="181"/>
       <c r="Q3" s="109" t="s">
         <v>443</v>
       </c>
-      <c r="R3" s="185" t="s">
+      <c r="R3" s="184" t="s">
         <v>819</v>
       </c>
-      <c r="S3" s="185"/>
-      <c r="T3" s="185"/>
-      <c r="U3" s="185"/>
-      <c r="V3" s="184"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="184"/>
+      <c r="U3" s="184"/>
+      <c r="V3" s="183"/>
       <c r="W3" s="109"/>
-      <c r="X3" s="183" t="s">
+      <c r="X3" s="182" t="s">
         <v>820</v>
       </c>
-      <c r="Y3" s="184"/>
-      <c r="Z3" s="183" t="s">
+      <c r="Y3" s="183"/>
+      <c r="Z3" s="182" t="s">
         <v>444</v>
       </c>
-      <c r="AA3" s="185"/>
-      <c r="AB3" s="185"/>
-      <c r="AC3" s="184"/>
-      <c r="AD3" s="183" t="s">
+      <c r="AA3" s="184"/>
+      <c r="AB3" s="184"/>
+      <c r="AC3" s="183"/>
+      <c r="AD3" s="182" t="s">
         <v>445</v>
       </c>
-      <c r="AE3" s="185"/>
-      <c r="AF3" s="184"/>
-      <c r="AG3" s="183" t="s">
+      <c r="AE3" s="184"/>
+      <c r="AF3" s="183"/>
+      <c r="AG3" s="182" t="s">
         <v>446</v>
       </c>
-      <c r="AH3" s="184"/>
+      <c r="AH3" s="183"/>
       <c r="AI3" s="102"/>
       <c r="AJ3" s="103"/>
       <c r="AK3" s="103"/>
@@ -10105,16 +10105,16 @@
       <c r="BJ3" s="98"/>
       <c r="BK3" s="98"/>
       <c r="BL3" s="99"/>
-      <c r="BM3" s="175" t="s">
+      <c r="BM3" s="177" t="s">
         <v>1051</v>
       </c>
-      <c r="BN3" s="176"/>
-      <c r="BO3" s="175" t="s">
+      <c r="BN3" s="178"/>
+      <c r="BO3" s="177" t="s">
         <v>645</v>
       </c>
-      <c r="BP3" s="176"/>
-      <c r="BQ3" s="176"/>
-      <c r="BR3" s="177"/>
+      <c r="BP3" s="178"/>
+      <c r="BQ3" s="178"/>
+      <c r="BR3" s="179"/>
       <c r="BS3" s="83" t="s">
         <v>646</v>
       </c>
@@ -10122,16 +10122,16 @@
     <row r="4" spans="1:71" ht="37.799999999999997" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="120"/>
       <c r="B4" s="120"/>
-      <c r="C4" s="165" t="s">
+      <c r="C4" s="192" t="s">
         <v>365</v>
       </c>
-      <c r="D4" s="166"/>
-      <c r="E4" s="166"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="166"/>
-      <c r="J4" s="167"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="180"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
+      <c r="J4" s="181"/>
       <c r="K4" s="123" t="s">
         <v>366</v>
       </c>
@@ -10204,46 +10204,46 @@
       <c r="AH4" s="110" t="s">
         <v>451</v>
       </c>
-      <c r="AI4" s="172" t="s">
+      <c r="AI4" s="187" t="s">
         <v>647</v>
       </c>
-      <c r="AJ4" s="173"/>
-      <c r="AK4" s="173"/>
-      <c r="AL4" s="173"/>
-      <c r="AM4" s="173"/>
-      <c r="AN4" s="173"/>
-      <c r="AO4" s="173"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="173" t="s">
+      <c r="AJ4" s="188"/>
+      <c r="AK4" s="188"/>
+      <c r="AL4" s="188"/>
+      <c r="AM4" s="188"/>
+      <c r="AN4" s="188"/>
+      <c r="AO4" s="188"/>
+      <c r="AP4" s="189"/>
+      <c r="AQ4" s="188" t="s">
         <v>648</v>
       </c>
-      <c r="AR4" s="173"/>
-      <c r="AS4" s="173"/>
-      <c r="AT4" s="173"/>
-      <c r="AU4" s="173"/>
-      <c r="AV4" s="173"/>
-      <c r="AW4" s="173"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="172" t="s">
+      <c r="AR4" s="188"/>
+      <c r="AS4" s="188"/>
+      <c r="AT4" s="188"/>
+      <c r="AU4" s="188"/>
+      <c r="AV4" s="188"/>
+      <c r="AW4" s="188"/>
+      <c r="AX4" s="189"/>
+      <c r="AY4" s="187" t="s">
         <v>649</v>
       </c>
-      <c r="AZ4" s="173"/>
-      <c r="BA4" s="173"/>
-      <c r="BB4" s="173"/>
-      <c r="BC4" s="173"/>
-      <c r="BD4" s="174"/>
+      <c r="AZ4" s="188"/>
+      <c r="BA4" s="188"/>
+      <c r="BB4" s="188"/>
+      <c r="BC4" s="188"/>
+      <c r="BD4" s="189"/>
       <c r="BE4" s="107" t="s">
         <v>650</v>
       </c>
-      <c r="BF4" s="175" t="s">
+      <c r="BF4" s="177" t="s">
         <v>651</v>
       </c>
-      <c r="BG4" s="176"/>
-      <c r="BH4" s="176"/>
-      <c r="BI4" s="176"/>
-      <c r="BJ4" s="176"/>
-      <c r="BK4" s="176"/>
-      <c r="BL4" s="177"/>
+      <c r="BG4" s="178"/>
+      <c r="BH4" s="178"/>
+      <c r="BI4" s="178"/>
+      <c r="BJ4" s="178"/>
+      <c r="BK4" s="178"/>
+      <c r="BL4" s="179"/>
       <c r="BM4" s="83" t="s">
         <v>1078</v>
       </c>
@@ -12267,208 +12267,208 @@
       <c r="BS14" s="28"/>
     </row>
     <row r="15" spans="1:71" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="180" t="s">
+      <c r="A15" s="171" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="181"/>
-      <c r="C15" s="181"/>
-      <c r="D15" s="181"/>
-      <c r="E15" s="181"/>
-      <c r="F15" s="181"/>
-      <c r="G15" s="181"/>
-      <c r="H15" s="181"/>
-      <c r="I15" s="181"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="181"/>
-      <c r="L15" s="181"/>
-      <c r="M15" s="181"/>
-      <c r="N15" s="181"/>
-      <c r="O15" s="181"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="181"/>
-      <c r="R15" s="181"/>
-      <c r="S15" s="181"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="181"/>
-      <c r="AA15" s="181"/>
-      <c r="AB15" s="181"/>
-      <c r="AC15" s="181"/>
-      <c r="AD15" s="181"/>
-      <c r="AE15" s="181"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="181"/>
-      <c r="AH15" s="181"/>
-      <c r="AI15" s="181"/>
-      <c r="AJ15" s="181"/>
-      <c r="AK15" s="181"/>
-      <c r="AL15" s="181"/>
-      <c r="AM15" s="181"/>
-      <c r="AN15" s="181"/>
-      <c r="AO15" s="181"/>
-      <c r="AP15" s="181"/>
-      <c r="AQ15" s="181"/>
-      <c r="AR15" s="181"/>
-      <c r="AS15" s="181"/>
-      <c r="AT15" s="181"/>
-      <c r="AU15" s="181"/>
-      <c r="AV15" s="181"/>
-      <c r="AW15" s="181"/>
-      <c r="AX15" s="181"/>
-      <c r="AY15" s="181"/>
-      <c r="AZ15" s="181"/>
-      <c r="BA15" s="181"/>
-      <c r="BB15" s="181"/>
-      <c r="BC15" s="181"/>
-      <c r="BD15" s="181"/>
-      <c r="BE15" s="181"/>
-      <c r="BF15" s="181"/>
-      <c r="BG15" s="181"/>
-      <c r="BH15" s="181"/>
-      <c r="BI15" s="181"/>
-      <c r="BJ15" s="181"/>
-      <c r="BK15" s="181"/>
-      <c r="BL15" s="181"/>
-      <c r="BM15" s="181"/>
-      <c r="BN15" s="181"/>
-      <c r="BO15" s="181"/>
-      <c r="BP15" s="181"/>
-      <c r="BQ15" s="181"/>
-      <c r="BR15" s="181"/>
-      <c r="BS15" s="182"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="172"/>
+      <c r="F15" s="172"/>
+      <c r="G15" s="172"/>
+      <c r="H15" s="172"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="172"/>
+      <c r="L15" s="172"/>
+      <c r="M15" s="172"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="172"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="172"/>
+      <c r="R15" s="172"/>
+      <c r="S15" s="172"/>
+      <c r="T15" s="172"/>
+      <c r="U15" s="172"/>
+      <c r="V15" s="172"/>
+      <c r="W15" s="172"/>
+      <c r="X15" s="172"/>
+      <c r="Y15" s="172"/>
+      <c r="Z15" s="172"/>
+      <c r="AA15" s="172"/>
+      <c r="AB15" s="172"/>
+      <c r="AC15" s="172"/>
+      <c r="AD15" s="172"/>
+      <c r="AE15" s="172"/>
+      <c r="AF15" s="172"/>
+      <c r="AG15" s="172"/>
+      <c r="AH15" s="172"/>
+      <c r="AI15" s="172"/>
+      <c r="AJ15" s="172"/>
+      <c r="AK15" s="172"/>
+      <c r="AL15" s="172"/>
+      <c r="AM15" s="172"/>
+      <c r="AN15" s="172"/>
+      <c r="AO15" s="172"/>
+      <c r="AP15" s="172"/>
+      <c r="AQ15" s="172"/>
+      <c r="AR15" s="172"/>
+      <c r="AS15" s="172"/>
+      <c r="AT15" s="172"/>
+      <c r="AU15" s="172"/>
+      <c r="AV15" s="172"/>
+      <c r="AW15" s="172"/>
+      <c r="AX15" s="172"/>
+      <c r="AY15" s="172"/>
+      <c r="AZ15" s="172"/>
+      <c r="BA15" s="172"/>
+      <c r="BB15" s="172"/>
+      <c r="BC15" s="172"/>
+      <c r="BD15" s="172"/>
+      <c r="BE15" s="172"/>
+      <c r="BF15" s="172"/>
+      <c r="BG15" s="172"/>
+      <c r="BH15" s="172"/>
+      <c r="BI15" s="172"/>
+      <c r="BJ15" s="172"/>
+      <c r="BK15" s="172"/>
+      <c r="BL15" s="172"/>
+      <c r="BM15" s="172"/>
+      <c r="BN15" s="172"/>
+      <c r="BO15" s="172"/>
+      <c r="BP15" s="172"/>
+      <c r="BQ15" s="172"/>
+      <c r="BR15" s="172"/>
+      <c r="BS15" s="173"/>
     </row>
     <row r="16" spans="1:71" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
-      <c r="C16" s="169" t="s">
+      <c r="C16" s="194" t="s">
         <v>362</v>
       </c>
-      <c r="D16" s="170"/>
-      <c r="E16" s="170"/>
-      <c r="F16" s="170"/>
-      <c r="G16" s="170"/>
-      <c r="H16" s="170"/>
-      <c r="I16" s="170"/>
-      <c r="J16" s="170"/>
-      <c r="K16" s="170"/>
-      <c r="L16" s="170"/>
-      <c r="M16" s="170"/>
-      <c r="N16" s="170"/>
-      <c r="O16" s="170"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="189" t="s">
+      <c r="D16" s="195"/>
+      <c r="E16" s="195"/>
+      <c r="F16" s="195"/>
+      <c r="G16" s="195"/>
+      <c r="H16" s="195"/>
+      <c r="I16" s="195"/>
+      <c r="J16" s="195"/>
+      <c r="K16" s="195"/>
+      <c r="L16" s="195"/>
+      <c r="M16" s="195"/>
+      <c r="N16" s="195"/>
+      <c r="O16" s="195"/>
+      <c r="P16" s="196"/>
+      <c r="Q16" s="185" t="s">
         <v>442</v>
       </c>
-      <c r="R16" s="190"/>
-      <c r="S16" s="190"/>
-      <c r="T16" s="190"/>
-      <c r="U16" s="190"/>
-      <c r="V16" s="190"/>
-      <c r="W16" s="190"/>
-      <c r="X16" s="190"/>
-      <c r="Y16" s="190"/>
-      <c r="Z16" s="190"/>
-      <c r="AA16" s="190"/>
-      <c r="AB16" s="190"/>
-      <c r="AC16" s="190"/>
-      <c r="AD16" s="190"/>
-      <c r="AE16" s="190"/>
-      <c r="AF16" s="190"/>
-      <c r="AG16" s="190"/>
-      <c r="AH16" s="190"/>
-      <c r="AI16" s="186"/>
-      <c r="AJ16" s="186"/>
-      <c r="AK16" s="186"/>
-      <c r="AL16" s="186"/>
-      <c r="AM16" s="186"/>
-      <c r="AN16" s="186"/>
-      <c r="AO16" s="186"/>
-      <c r="AP16" s="186"/>
-      <c r="AQ16" s="186"/>
-      <c r="AR16" s="186"/>
-      <c r="AS16" s="186"/>
-      <c r="AT16" s="186"/>
-      <c r="AU16" s="186"/>
-      <c r="AV16" s="186"/>
-      <c r="AW16" s="186"/>
-      <c r="AX16" s="186"/>
-      <c r="AY16" s="186"/>
-      <c r="AZ16" s="186"/>
-      <c r="BA16" s="186"/>
-      <c r="BB16" s="186"/>
-      <c r="BC16" s="186"/>
-      <c r="BD16" s="186"/>
-      <c r="BE16" s="186"/>
-      <c r="BF16" s="187"/>
-      <c r="BG16" s="188"/>
-      <c r="BH16" s="188"/>
-      <c r="BI16" s="188"/>
-      <c r="BJ16" s="188"/>
-      <c r="BK16" s="188"/>
-      <c r="BL16" s="188"/>
-      <c r="BM16" s="188"/>
-      <c r="BN16" s="188"/>
-      <c r="BO16" s="188"/>
-      <c r="BP16" s="188"/>
-      <c r="BQ16" s="188"/>
-      <c r="BR16" s="188"/>
-      <c r="BS16" s="188"/>
+      <c r="R16" s="186"/>
+      <c r="S16" s="186"/>
+      <c r="T16" s="186"/>
+      <c r="U16" s="186"/>
+      <c r="V16" s="186"/>
+      <c r="W16" s="186"/>
+      <c r="X16" s="186"/>
+      <c r="Y16" s="186"/>
+      <c r="Z16" s="186"/>
+      <c r="AA16" s="186"/>
+      <c r="AB16" s="186"/>
+      <c r="AC16" s="186"/>
+      <c r="AD16" s="186"/>
+      <c r="AE16" s="186"/>
+      <c r="AF16" s="186"/>
+      <c r="AG16" s="186"/>
+      <c r="AH16" s="186"/>
+      <c r="AI16" s="174"/>
+      <c r="AJ16" s="174"/>
+      <c r="AK16" s="174"/>
+      <c r="AL16" s="174"/>
+      <c r="AM16" s="174"/>
+      <c r="AN16" s="174"/>
+      <c r="AO16" s="174"/>
+      <c r="AP16" s="174"/>
+      <c r="AQ16" s="174"/>
+      <c r="AR16" s="174"/>
+      <c r="AS16" s="174"/>
+      <c r="AT16" s="174"/>
+      <c r="AU16" s="174"/>
+      <c r="AV16" s="174"/>
+      <c r="AW16" s="174"/>
+      <c r="AX16" s="174"/>
+      <c r="AY16" s="174"/>
+      <c r="AZ16" s="174"/>
+      <c r="BA16" s="174"/>
+      <c r="BB16" s="174"/>
+      <c r="BC16" s="174"/>
+      <c r="BD16" s="174"/>
+      <c r="BE16" s="174"/>
+      <c r="BF16" s="175"/>
+      <c r="BG16" s="176"/>
+      <c r="BH16" s="176"/>
+      <c r="BI16" s="176"/>
+      <c r="BJ16" s="176"/>
+      <c r="BK16" s="176"/>
+      <c r="BL16" s="176"/>
+      <c r="BM16" s="176"/>
+      <c r="BN16" s="176"/>
+      <c r="BO16" s="176"/>
+      <c r="BP16" s="176"/>
+      <c r="BQ16" s="176"/>
+      <c r="BR16" s="176"/>
+      <c r="BS16" s="176"/>
     </row>
     <row r="17" spans="1:71" ht="25.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
-      <c r="C17" s="165" t="s">
+      <c r="C17" s="192" t="s">
         <v>363</v>
       </c>
-      <c r="D17" s="166"/>
-      <c r="E17" s="166"/>
-      <c r="F17" s="166"/>
-      <c r="G17" s="166"/>
-      <c r="H17" s="166"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="166"/>
-      <c r="L17" s="166" t="s">
+      <c r="D17" s="180"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="180"/>
+      <c r="G17" s="180"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="180"/>
+      <c r="J17" s="180"/>
+      <c r="K17" s="180"/>
+      <c r="L17" s="180" t="s">
         <v>364</v>
       </c>
-      <c r="M17" s="166"/>
-      <c r="N17" s="166"/>
-      <c r="O17" s="166"/>
-      <c r="P17" s="167"/>
+      <c r="M17" s="180"/>
+      <c r="N17" s="180"/>
+      <c r="O17" s="180"/>
+      <c r="P17" s="181"/>
       <c r="Q17" s="109" t="s">
         <v>443</v>
       </c>
-      <c r="R17" s="185" t="s">
+      <c r="R17" s="184" t="s">
         <v>819</v>
       </c>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
-      <c r="V17" s="184"/>
+      <c r="S17" s="184"/>
+      <c r="T17" s="184"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="183"/>
       <c r="W17" s="109"/>
-      <c r="X17" s="183" t="s">
+      <c r="X17" s="182" t="s">
         <v>820</v>
       </c>
-      <c r="Y17" s="184"/>
-      <c r="Z17" s="183" t="s">
+      <c r="Y17" s="183"/>
+      <c r="Z17" s="182" t="s">
         <v>444</v>
       </c>
-      <c r="AA17" s="185"/>
-      <c r="AB17" s="185"/>
-      <c r="AC17" s="184"/>
-      <c r="AD17" s="183" t="s">
+      <c r="AA17" s="184"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="183"/>
+      <c r="AD17" s="182" t="s">
         <v>445</v>
       </c>
-      <c r="AE17" s="185"/>
-      <c r="AF17" s="184"/>
-      <c r="AG17" s="183" t="s">
+      <c r="AE17" s="184"/>
+      <c r="AF17" s="183"/>
+      <c r="AG17" s="182" t="s">
         <v>446</v>
       </c>
-      <c r="AH17" s="184"/>
+      <c r="AH17" s="183"/>
       <c r="AI17" s="102"/>
       <c r="AJ17" s="103"/>
       <c r="AK17" s="103"/>
@@ -12499,16 +12499,16 @@
       <c r="BJ17" s="98"/>
       <c r="BK17" s="98"/>
       <c r="BL17" s="99"/>
-      <c r="BM17" s="175" t="s">
+      <c r="BM17" s="177" t="s">
         <v>1051</v>
       </c>
-      <c r="BN17" s="176"/>
-      <c r="BO17" s="175" t="s">
+      <c r="BN17" s="178"/>
+      <c r="BO17" s="177" t="s">
         <v>645</v>
       </c>
-      <c r="BP17" s="176"/>
-      <c r="BQ17" s="176"/>
-      <c r="BR17" s="177"/>
+      <c r="BP17" s="178"/>
+      <c r="BQ17" s="178"/>
+      <c r="BR17" s="179"/>
       <c r="BS17" s="83" t="s">
         <v>646</v>
       </c>
@@ -12520,16 +12520,16 @@
       <c r="B18" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="165" t="s">
+      <c r="C18" s="192" t="s">
         <v>365</v>
       </c>
-      <c r="D18" s="166"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="166"/>
-      <c r="G18" s="166"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="167"/>
+      <c r="D18" s="180"/>
+      <c r="E18" s="180"/>
+      <c r="F18" s="180"/>
+      <c r="G18" s="180"/>
+      <c r="H18" s="180"/>
+      <c r="I18" s="180"/>
+      <c r="J18" s="181"/>
       <c r="K18" s="123" t="s">
         <v>421</v>
       </c>
@@ -12602,44 +12602,44 @@
       <c r="AH18" s="110" t="s">
         <v>451</v>
       </c>
-      <c r="AI18" s="172" t="s">
+      <c r="AI18" s="187" t="s">
         <v>647</v>
       </c>
-      <c r="AJ18" s="173"/>
-      <c r="AK18" s="173"/>
-      <c r="AL18" s="173"/>
-      <c r="AM18" s="173"/>
-      <c r="AN18" s="173"/>
-      <c r="AO18" s="173"/>
-      <c r="AP18" s="174"/>
-      <c r="AQ18" s="173"/>
-      <c r="AR18" s="173"/>
-      <c r="AS18" s="173"/>
-      <c r="AT18" s="173"/>
-      <c r="AU18" s="173"/>
-      <c r="AV18" s="173"/>
-      <c r="AW18" s="173"/>
-      <c r="AX18" s="174"/>
-      <c r="AY18" s="172" t="s">
+      <c r="AJ18" s="188"/>
+      <c r="AK18" s="188"/>
+      <c r="AL18" s="188"/>
+      <c r="AM18" s="188"/>
+      <c r="AN18" s="188"/>
+      <c r="AO18" s="188"/>
+      <c r="AP18" s="189"/>
+      <c r="AQ18" s="188"/>
+      <c r="AR18" s="188"/>
+      <c r="AS18" s="188"/>
+      <c r="AT18" s="188"/>
+      <c r="AU18" s="188"/>
+      <c r="AV18" s="188"/>
+      <c r="AW18" s="188"/>
+      <c r="AX18" s="189"/>
+      <c r="AY18" s="187" t="s">
         <v>649</v>
       </c>
-      <c r="AZ18" s="173"/>
-      <c r="BA18" s="173"/>
-      <c r="BB18" s="173"/>
-      <c r="BC18" s="173"/>
-      <c r="BD18" s="174"/>
+      <c r="AZ18" s="188"/>
+      <c r="BA18" s="188"/>
+      <c r="BB18" s="188"/>
+      <c r="BC18" s="188"/>
+      <c r="BD18" s="189"/>
       <c r="BE18" s="105" t="s">
         <v>650</v>
       </c>
-      <c r="BF18" s="175" t="s">
+      <c r="BF18" s="177" t="s">
         <v>651</v>
       </c>
-      <c r="BG18" s="176"/>
-      <c r="BH18" s="176"/>
-      <c r="BI18" s="176"/>
-      <c r="BJ18" s="176"/>
-      <c r="BK18" s="176"/>
-      <c r="BL18" s="177"/>
+      <c r="BG18" s="178"/>
+      <c r="BH18" s="178"/>
+      <c r="BI18" s="178"/>
+      <c r="BJ18" s="178"/>
+      <c r="BK18" s="178"/>
+      <c r="BL18" s="179"/>
       <c r="BM18" s="83" t="s">
         <v>1078</v>
       </c>
@@ -16093,24 +16093,47 @@
       </c>
     </row>
     <row r="36" spans="1:71" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AY36" s="213" t="s">
+      <c r="C36" s="169" t="s">
         <v>1096</v>
       </c>
-      <c r="AZ36" s="212"/>
-      <c r="BA36" s="212"/>
-      <c r="BB36" s="212"/>
-      <c r="BC36" s="212"/>
+      <c r="D36" s="170"/>
+      <c r="E36" s="170"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="170"/>
     </row>
     <row r="37" spans="1:71" x14ac:dyDescent="0.55000000000000004">
-      <c r="AY37" s="212"/>
-      <c r="AZ37" s="212"/>
-      <c r="BA37" s="212"/>
-      <c r="BB37" s="212"/>
-      <c r="BC37" s="212"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="170"/>
+      <c r="E37" s="170"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="AY36:BC37"/>
+    <mergeCell ref="A15:BS15"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="Q2:AH2"/>
+    <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C2:P2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="L3:P3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C16:P16"/>
+    <mergeCell ref="AI2:BE2"/>
+    <mergeCell ref="BF2:BS2"/>
+    <mergeCell ref="BM3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AI4:AP4"/>
+    <mergeCell ref="AQ4:AX4"/>
+    <mergeCell ref="AY4:BD4"/>
+    <mergeCell ref="BF4:BL4"/>
+    <mergeCell ref="AG17:AH17"/>
+    <mergeCell ref="AI18:AP18"/>
+    <mergeCell ref="AQ18:AX18"/>
+    <mergeCell ref="AY18:BD18"/>
+    <mergeCell ref="BF18:BL18"/>
+    <mergeCell ref="C36:G37"/>
     <mergeCell ref="A1:BS1"/>
     <mergeCell ref="AI16:BE16"/>
     <mergeCell ref="BF16:BS16"/>
@@ -16126,29 +16149,6 @@
     <mergeCell ref="Q16:AH16"/>
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="AD17:AF17"/>
-    <mergeCell ref="AG17:AH17"/>
-    <mergeCell ref="AI18:AP18"/>
-    <mergeCell ref="AQ18:AX18"/>
-    <mergeCell ref="AY18:BD18"/>
-    <mergeCell ref="BF18:BL18"/>
-    <mergeCell ref="AI2:BE2"/>
-    <mergeCell ref="BF2:BS2"/>
-    <mergeCell ref="BM3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AI4:AP4"/>
-    <mergeCell ref="AQ4:AX4"/>
-    <mergeCell ref="AY4:BD4"/>
-    <mergeCell ref="BF4:BL4"/>
-    <mergeCell ref="A15:BS15"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="Q2:AH2"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="C2:P2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C16:P16"/>
   </mergeCells>
   <conditionalFormatting sqref="B28:B29">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -16190,12 +16190,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="200" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="196"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="202"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A2" s="80" t="s">
@@ -16252,15 +16252,15 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A7" s="175" t="s">
+      <c r="A7" s="177" t="s">
         <v>362</v>
       </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="177"/>
+      <c r="B7" s="178"/>
+      <c r="C7" s="178"/>
+      <c r="D7" s="179"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A8" s="216" t="s">
+      <c r="A8" s="137" t="s">
         <v>821</v>
       </c>
       <c r="B8" s="136" t="s">
@@ -16274,7 +16274,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="50.4" x14ac:dyDescent="0.5">
-      <c r="A9" s="217" t="s">
+      <c r="A9" s="205" t="s">
         <v>835</v>
       </c>
       <c r="B9" s="136" t="s">
@@ -16288,7 +16288,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A10" s="217"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="136" t="s">
         <v>374</v>
       </c>
@@ -16300,7 +16300,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A11" s="217"/>
+      <c r="A11" s="205"/>
       <c r="B11" s="136" t="s">
         <v>1070</v>
       </c>
@@ -16312,7 +16312,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="63" x14ac:dyDescent="0.5">
-      <c r="A12" s="217"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="136" t="s">
         <v>375</v>
       </c>
@@ -16324,7 +16324,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A13" s="217"/>
+      <c r="A13" s="205"/>
       <c r="B13" s="136" t="s">
         <v>377</v>
       </c>
@@ -16336,11 +16336,11 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A14" s="217"/>
+      <c r="A14" s="205"/>
       <c r="B14" s="136" t="s">
         <v>424</v>
       </c>
-      <c r="C14" s="218" t="s">
+      <c r="C14" s="138" t="s">
         <v>844</v>
       </c>
       <c r="D14" s="84" t="s">
@@ -16348,11 +16348,11 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A15" s="217"/>
+      <c r="A15" s="205"/>
       <c r="B15" s="136" t="s">
         <v>380</v>
       </c>
-      <c r="C15" s="218" t="s">
+      <c r="C15" s="138" t="s">
         <v>845</v>
       </c>
       <c r="D15" s="84" t="s">
@@ -16360,7 +16360,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A16" s="217"/>
+      <c r="A16" s="205"/>
       <c r="B16" s="136" t="s">
         <v>381</v>
       </c>
@@ -16372,7 +16372,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A17" s="219" t="s">
+      <c r="A17" s="206" t="s">
         <v>366</v>
       </c>
       <c r="B17" s="87" t="s">
@@ -16386,7 +16386,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A18" s="217"/>
+      <c r="A18" s="205"/>
       <c r="B18" s="87" t="s">
         <v>849</v>
       </c>
@@ -16398,7 +16398,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A19" s="217"/>
+      <c r="A19" s="205"/>
       <c r="B19" s="87" t="s">
         <v>400</v>
       </c>
@@ -16410,7 +16410,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A20" s="217"/>
+      <c r="A20" s="205"/>
       <c r="B20" s="87" t="s">
         <v>853</v>
       </c>
@@ -16422,7 +16422,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A21" s="217"/>
+      <c r="A21" s="205"/>
       <c r="B21" s="87" t="s">
         <v>855</v>
       </c>
@@ -16434,7 +16434,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A22" s="217"/>
+      <c r="A22" s="205"/>
       <c r="B22" s="87" t="s">
         <v>417</v>
       </c>
@@ -16446,7 +16446,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A23" s="220"/>
+      <c r="A23" s="207"/>
       <c r="B23" s="87" t="s">
         <v>317</v>
       </c>
@@ -16458,7 +16458,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A24" s="205" t="s">
+      <c r="A24" s="208" t="s">
         <v>367</v>
       </c>
       <c r="B24" s="136" t="s">
@@ -16472,55 +16472,55 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A25" s="206"/>
+      <c r="A25" s="209"/>
       <c r="B25" s="87" t="s">
         <v>863</v>
       </c>
       <c r="C25" s="84" t="s">
         <v>864</v>
       </c>
-      <c r="D25" s="221" t="s">
+      <c r="D25" s="139" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A26" s="206"/>
+      <c r="A26" s="209"/>
       <c r="B26" s="87" t="s">
         <v>866</v>
       </c>
       <c r="C26" s="84" t="s">
         <v>867</v>
       </c>
-      <c r="D26" s="221" t="s">
+      <c r="D26" s="139" t="s">
         <v>868</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="25.5" x14ac:dyDescent="0.5">
-      <c r="A27" s="206"/>
+      <c r="A27" s="209"/>
       <c r="B27" s="87" t="s">
         <v>869</v>
       </c>
       <c r="C27" s="84" t="s">
         <v>870</v>
       </c>
-      <c r="D27" s="218" t="s">
+      <c r="D27" s="138" t="s">
         <v>871</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A28" s="207"/>
+      <c r="A28" s="210"/>
       <c r="B28" s="87" t="s">
         <v>317</v>
       </c>
       <c r="C28" s="84" t="s">
         <v>872</v>
       </c>
-      <c r="D28" s="221" t="s">
+      <c r="D28" s="139" t="s">
         <v>873</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A29" s="216" t="s">
+      <c r="A29" s="137" t="s">
         <v>368</v>
       </c>
       <c r="B29" s="87" t="s">
@@ -16534,7 +16534,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A30" s="205" t="s">
+      <c r="A30" s="208" t="s">
         <v>369</v>
       </c>
       <c r="B30" s="136" t="s">
@@ -16548,7 +16548,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A31" s="206"/>
+      <c r="A31" s="209"/>
       <c r="B31" s="87" t="s">
         <v>399</v>
       </c>
@@ -16560,7 +16560,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A32" s="206"/>
+      <c r="A32" s="209"/>
       <c r="B32" s="87" t="s">
         <v>427</v>
       </c>
@@ -16572,7 +16572,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A33" s="206"/>
+      <c r="A33" s="209"/>
       <c r="B33" s="87" t="s">
         <v>401</v>
       </c>
@@ -16584,7 +16584,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A34" s="206"/>
+      <c r="A34" s="209"/>
       <c r="B34" s="87" t="s">
         <v>884</v>
       </c>
@@ -16596,7 +16596,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A35" s="206"/>
+      <c r="A35" s="209"/>
       <c r="B35" s="87" t="s">
         <v>419</v>
       </c>
@@ -16608,7 +16608,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="25.2" x14ac:dyDescent="0.5">
-      <c r="A36" s="206"/>
+      <c r="A36" s="209"/>
       <c r="B36" s="87" t="s">
         <v>889</v>
       </c>
@@ -16620,31 +16620,31 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37" s="206"/>
-      <c r="B37" s="222" t="s">
+      <c r="A37" s="209"/>
+      <c r="B37" s="140" t="s">
         <v>381</v>
       </c>
-      <c r="C37" s="218" t="s">
+      <c r="C37" s="138" t="s">
         <v>452</v>
       </c>
-      <c r="D37" s="218" t="s">
+      <c r="D37" s="138" t="s">
         <v>892</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="25.5" x14ac:dyDescent="0.5">
-      <c r="A38" s="207"/>
-      <c r="B38" s="222" t="s">
-        <v>317</v>
-      </c>
-      <c r="C38" s="218" t="s">
+      <c r="A38" s="210"/>
+      <c r="B38" s="140" t="s">
+        <v>317</v>
+      </c>
+      <c r="C38" s="138" t="s">
         <v>893</v>
       </c>
-      <c r="D38" s="218" t="s">
+      <c r="D38" s="138" t="s">
         <v>894</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="50.4" x14ac:dyDescent="0.5">
-      <c r="A39" s="216" t="s">
+      <c r="A39" s="137" t="s">
         <v>895</v>
       </c>
       <c r="B39" s="87" t="s">
@@ -16658,7 +16658,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="37.799999999999997" x14ac:dyDescent="0.5">
-      <c r="A40" s="216" t="s">
+      <c r="A40" s="137" t="s">
         <v>898</v>
       </c>
       <c r="B40" s="87" t="s">
@@ -16672,12 +16672,12 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="194" t="s">
+      <c r="A42" s="200" t="s">
         <v>900</v>
       </c>
-      <c r="B42" s="195"/>
-      <c r="C42" s="195"/>
-      <c r="D42" s="196"/>
+      <c r="B42" s="201"/>
+      <c r="C42" s="201"/>
+      <c r="D42" s="202"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43" s="80" t="s">
@@ -16708,7 +16708,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="70.5" x14ac:dyDescent="0.5">
-      <c r="A45" s="192" t="s">
+      <c r="A45" s="198" t="s">
         <v>819</v>
       </c>
       <c r="B45" s="80" t="s">
@@ -16722,7 +16722,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" ht="70.5" x14ac:dyDescent="0.5">
-      <c r="A46" s="192"/>
+      <c r="A46" s="198"/>
       <c r="B46" s="80" t="s">
         <v>757</v>
       </c>
@@ -16734,7 +16734,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" ht="56.4" x14ac:dyDescent="0.5">
-      <c r="A47" s="192"/>
+      <c r="A47" s="198"/>
       <c r="B47" s="80" t="s">
         <v>759</v>
       </c>
@@ -16746,7 +16746,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" ht="70.5" x14ac:dyDescent="0.5">
-      <c r="A48" s="192"/>
+      <c r="A48" s="198"/>
       <c r="B48" s="80" t="s">
         <v>906</v>
       </c>
@@ -16758,7 +16758,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="70.5" x14ac:dyDescent="0.5">
-      <c r="A49" s="193"/>
+      <c r="A49" s="199"/>
       <c r="B49" s="80" t="s">
         <v>907</v>
       </c>
@@ -16784,7 +16784,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="28.2" x14ac:dyDescent="0.5">
-      <c r="A51" s="208" t="s">
+      <c r="A51" s="211" t="s">
         <v>820</v>
       </c>
       <c r="B51" s="89" t="s">
@@ -16798,7 +16798,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A52" s="209"/>
+      <c r="A52" s="212"/>
       <c r="B52" s="89" t="s">
         <v>11</v>
       </c>
@@ -16810,7 +16810,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A53" s="191" t="s">
+      <c r="A53" s="197" t="s">
         <v>444</v>
       </c>
       <c r="B53" s="89" t="s">
@@ -16824,7 +16824,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A54" s="192"/>
+      <c r="A54" s="198"/>
       <c r="B54" s="89" t="s">
         <v>448</v>
       </c>
@@ -16836,7 +16836,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A55" s="192"/>
+      <c r="A55" s="198"/>
       <c r="B55" s="89" t="s">
         <v>449</v>
       </c>
@@ -16848,7 +16848,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A56" s="193"/>
+      <c r="A56" s="199"/>
       <c r="B56" s="89" t="s">
         <v>449</v>
       </c>
@@ -16860,7 +16860,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="42.3" x14ac:dyDescent="0.5">
-      <c r="A57" s="191" t="s">
+      <c r="A57" s="197" t="s">
         <v>445</v>
       </c>
       <c r="B57" s="89" t="s">
@@ -16874,7 +16874,7 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A58" s="192"/>
+      <c r="A58" s="198"/>
       <c r="B58" s="89" t="s">
         <v>13</v>
       </c>
@@ -16886,7 +16886,7 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="28.2" x14ac:dyDescent="0.5">
-      <c r="A59" s="193"/>
+      <c r="A59" s="199"/>
       <c r="B59" s="89" t="s">
         <v>14</v>
       </c>
@@ -16898,7 +16898,7 @@
       </c>
     </row>
     <row r="60" spans="1:4" ht="28.2" x14ac:dyDescent="0.5">
-      <c r="A60" s="191" t="s">
+      <c r="A60" s="197" t="s">
         <v>446</v>
       </c>
       <c r="B60" s="89" t="s">
@@ -16912,7 +16912,7 @@
       </c>
     </row>
     <row r="61" spans="1:4" ht="28.2" x14ac:dyDescent="0.5">
-      <c r="A61" s="193"/>
+      <c r="A61" s="199"/>
       <c r="B61" s="89" t="s">
         <v>451</v>
       </c>
@@ -16930,170 +16930,170 @@
       <c r="D62" s="91"/>
     </row>
     <row r="63" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="194" t="s">
+      <c r="A63" s="200" t="s">
         <v>925</v>
       </c>
-      <c r="B63" s="195"/>
-      <c r="C63" s="195"/>
-      <c r="D63" s="196"/>
+      <c r="B63" s="201"/>
+      <c r="C63" s="201"/>
+      <c r="D63" s="202"/>
     </row>
     <row r="64" spans="1:4" ht="14.4" x14ac:dyDescent="0.5">
-      <c r="A64" s="194" t="s">
+      <c r="A64" s="200" t="s">
         <v>926</v>
       </c>
-      <c r="B64" s="196"/>
-      <c r="C64" s="201" t="s">
+      <c r="B64" s="202"/>
+      <c r="C64" s="213" t="s">
         <v>927</v>
       </c>
-      <c r="D64" s="202"/>
+      <c r="D64" s="214"/>
     </row>
     <row r="65" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="197" t="s">
+      <c r="A65" s="215" t="s">
         <v>729</v>
       </c>
-      <c r="B65" s="198"/>
-      <c r="C65" s="199" t="s">
+      <c r="B65" s="216"/>
+      <c r="C65" s="217" t="s">
         <v>928</v>
       </c>
-      <c r="D65" s="200"/>
+      <c r="D65" s="218"/>
     </row>
     <row r="66" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="197" t="s">
+      <c r="A66" s="215" t="s">
         <v>498</v>
       </c>
-      <c r="B66" s="198"/>
-      <c r="C66" s="199" t="s">
+      <c r="B66" s="216"/>
+      <c r="C66" s="217" t="s">
         <v>929</v>
       </c>
-      <c r="D66" s="200"/>
+      <c r="D66" s="218"/>
     </row>
     <row r="67" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A67" s="197" t="s">
+      <c r="A67" s="215" t="s">
         <v>734</v>
       </c>
-      <c r="B67" s="198"/>
-      <c r="C67" s="199" t="s">
+      <c r="B67" s="216"/>
+      <c r="C67" s="217" t="s">
         <v>930</v>
       </c>
-      <c r="D67" s="200"/>
+      <c r="D67" s="218"/>
     </row>
     <row r="68" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A68" s="197" t="s">
+      <c r="A68" s="215" t="s">
         <v>736</v>
       </c>
-      <c r="B68" s="198"/>
-      <c r="C68" s="199" t="s">
+      <c r="B68" s="216"/>
+      <c r="C68" s="217" t="s">
         <v>931</v>
       </c>
-      <c r="D68" s="200"/>
+      <c r="D68" s="218"/>
     </row>
     <row r="69" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A69" s="197" t="s">
+      <c r="A69" s="215" t="s">
         <v>739</v>
       </c>
-      <c r="B69" s="198"/>
-      <c r="C69" s="199" t="s">
+      <c r="B69" s="216"/>
+      <c r="C69" s="217" t="s">
         <v>932</v>
       </c>
-      <c r="D69" s="200"/>
+      <c r="D69" s="218"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A70" s="197" t="s">
+      <c r="A70" s="215" t="s">
         <v>741</v>
       </c>
-      <c r="B70" s="198"/>
-      <c r="C70" s="199" t="s">
+      <c r="B70" s="216"/>
+      <c r="C70" s="217" t="s">
         <v>933</v>
       </c>
-      <c r="D70" s="200"/>
+      <c r="D70" s="218"/>
     </row>
     <row r="71" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A71" s="197" t="s">
+      <c r="A71" s="215" t="s">
         <v>743</v>
       </c>
-      <c r="B71" s="198"/>
-      <c r="C71" s="199" t="s">
+      <c r="B71" s="216"/>
+      <c r="C71" s="217" t="s">
         <v>934</v>
       </c>
-      <c r="D71" s="200"/>
+      <c r="D71" s="218"/>
     </row>
     <row r="72" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A72" s="197" t="s">
+      <c r="A72" s="215" t="s">
         <v>935</v>
       </c>
-      <c r="B72" s="198"/>
-      <c r="C72" s="199" t="s">
+      <c r="B72" s="216"/>
+      <c r="C72" s="217" t="s">
         <v>936</v>
       </c>
-      <c r="D72" s="200"/>
+      <c r="D72" s="218"/>
     </row>
     <row r="73" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A73" s="197" t="s">
+      <c r="A73" s="215" t="s">
         <v>745</v>
       </c>
-      <c r="B73" s="198"/>
-      <c r="C73" s="199" t="s">
+      <c r="B73" s="216"/>
+      <c r="C73" s="217" t="s">
         <v>937</v>
       </c>
-      <c r="D73" s="200"/>
+      <c r="D73" s="218"/>
     </row>
     <row r="74" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="197" t="s">
+      <c r="A74" s="215" t="s">
         <v>938</v>
       </c>
-      <c r="B74" s="198"/>
-      <c r="C74" s="199" t="s">
+      <c r="B74" s="216"/>
+      <c r="C74" s="217" t="s">
         <v>939</v>
       </c>
-      <c r="D74" s="200"/>
+      <c r="D74" s="218"/>
     </row>
     <row r="75" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A75" s="197" t="s">
+      <c r="A75" s="215" t="s">
         <v>940</v>
       </c>
-      <c r="B75" s="198"/>
-      <c r="C75" s="199" t="s">
+      <c r="B75" s="216"/>
+      <c r="C75" s="217" t="s">
         <v>941</v>
       </c>
-      <c r="D75" s="200"/>
+      <c r="D75" s="218"/>
     </row>
     <row r="76" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A76" s="197" t="s">
+      <c r="A76" s="215" t="s">
         <v>747</v>
       </c>
-      <c r="B76" s="198"/>
-      <c r="C76" s="199" t="s">
+      <c r="B76" s="216"/>
+      <c r="C76" s="217" t="s">
         <v>942</v>
       </c>
-      <c r="D76" s="200"/>
+      <c r="D76" s="218"/>
     </row>
     <row r="77" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A77" s="197" t="s">
+      <c r="A77" s="215" t="s">
         <v>749</v>
       </c>
-      <c r="B77" s="198"/>
-      <c r="C77" s="199" t="s">
+      <c r="B77" s="216"/>
+      <c r="C77" s="217" t="s">
         <v>943</v>
       </c>
-      <c r="D77" s="200"/>
+      <c r="D77" s="218"/>
     </row>
     <row r="78" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A78" s="197" t="s">
+      <c r="A78" s="215" t="s">
         <v>944</v>
       </c>
-      <c r="B78" s="198"/>
-      <c r="C78" s="199" t="s">
+      <c r="B78" s="216"/>
+      <c r="C78" s="217" t="s">
         <v>945</v>
       </c>
-      <c r="D78" s="200"/>
+      <c r="D78" s="218"/>
     </row>
     <row r="80" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A80" s="194" t="s">
+      <c r="A80" s="200" t="s">
         <v>946</v>
       </c>
-      <c r="B80" s="195"/>
-      <c r="C80" s="195"/>
-      <c r="D80" s="196"/>
+      <c r="B80" s="201"/>
+      <c r="C80" s="201"/>
+      <c r="D80" s="202"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A81" s="80" t="s">
@@ -17110,18 +17110,18 @@
       </c>
     </row>
     <row r="82" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A82" s="194" t="s">
+      <c r="A82" s="200" t="s">
         <v>647</v>
       </c>
-      <c r="B82" s="195"/>
-      <c r="C82" s="195"/>
-      <c r="D82" s="195"/>
+      <c r="B82" s="201"/>
+      <c r="C82" s="201"/>
+      <c r="D82" s="201"/>
     </row>
     <row r="83" spans="1:13" ht="28.2" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A83" s="175" t="s">
+      <c r="A83" s="177" t="s">
         <v>947</v>
       </c>
-      <c r="B83" s="177"/>
+      <c r="B83" s="179"/>
       <c r="C83" s="61" t="s">
         <v>948</v>
       </c>
@@ -17246,12 +17246,12 @@
       <c r="M91" s="94"/>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.5">
-      <c r="A92" s="195" t="s">
+      <c r="A92" s="201" t="s">
         <v>648</v>
       </c>
-      <c r="B92" s="195"/>
-      <c r="C92" s="195"/>
-      <c r="D92" s="196"/>
+      <c r="B92" s="201"/>
+      <c r="C92" s="201"/>
+      <c r="D92" s="202"/>
       <c r="F92" s="94"/>
       <c r="G92" s="94"/>
       <c r="H92" s="94"/>
@@ -17262,10 +17262,10 @@
       <c r="M92" s="94"/>
     </row>
     <row r="93" spans="1:13" ht="38.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A93" s="176" t="s">
+      <c r="A93" s="178" t="s">
         <v>969</v>
       </c>
-      <c r="B93" s="177"/>
+      <c r="B93" s="179"/>
       <c r="C93" s="61" t="s">
         <v>970</v>
       </c>
@@ -17400,18 +17400,18 @@
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.5">
-      <c r="A103" s="194" t="s">
+      <c r="A103" s="200" t="s">
         <v>649</v>
       </c>
-      <c r="B103" s="195"/>
-      <c r="C103" s="195"/>
-      <c r="D103" s="196"/>
+      <c r="B103" s="201"/>
+      <c r="C103" s="201"/>
+      <c r="D103" s="202"/>
     </row>
     <row r="104" spans="1:17" ht="28.2" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A104" s="175" t="s">
+      <c r="A104" s="177" t="s">
         <v>994</v>
       </c>
-      <c r="B104" s="177"/>
+      <c r="B104" s="179"/>
       <c r="C104" s="61" t="s">
         <v>995</v>
       </c>
@@ -17566,12 +17566,12 @@
       <c r="Q111" s="56"/>
     </row>
     <row r="113" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A113" s="194" t="s">
+      <c r="A113" s="200" t="s">
         <v>1015</v>
       </c>
-      <c r="B113" s="195"/>
-      <c r="C113" s="195"/>
-      <c r="D113" s="196"/>
+      <c r="B113" s="201"/>
+      <c r="C113" s="201"/>
+      <c r="D113" s="202"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.5">
       <c r="A114" s="80" t="s">
@@ -17588,18 +17588,18 @@
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.5">
-      <c r="A115" s="194" t="s">
+      <c r="A115" s="200" t="s">
         <v>1016</v>
       </c>
-      <c r="B115" s="195"/>
-      <c r="C115" s="195"/>
-      <c r="D115" s="196"/>
+      <c r="B115" s="201"/>
+      <c r="C115" s="201"/>
+      <c r="D115" s="202"/>
     </row>
     <row r="116" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A116" s="175" t="s">
+      <c r="A116" s="177" t="s">
         <v>1017</v>
       </c>
-      <c r="B116" s="177"/>
+      <c r="B116" s="179"/>
       <c r="C116" s="61" t="s">
         <v>1018</v>
       </c>
@@ -17706,7 +17706,7 @@
       </c>
     </row>
     <row r="124" spans="1:14" ht="56.4" x14ac:dyDescent="0.5">
-      <c r="A124" s="191" t="s">
+      <c r="A124" s="197" t="s">
         <v>1036</v>
       </c>
       <c r="B124" s="83" t="s">
@@ -17720,7 +17720,7 @@
       </c>
     </row>
     <row r="125" spans="1:14" ht="56.4" x14ac:dyDescent="0.5">
-      <c r="A125" s="192"/>
+      <c r="A125" s="198"/>
       <c r="B125" s="83" t="s">
         <v>652</v>
       </c>
@@ -17740,7 +17740,7 @@
       <c r="N125" s="94"/>
     </row>
     <row r="126" spans="1:14" ht="56.4" x14ac:dyDescent="0.5">
-      <c r="A126" s="191" t="s">
+      <c r="A126" s="197" t="s">
         <v>645</v>
       </c>
       <c r="B126" s="83" t="s">
@@ -17762,7 +17762,7 @@
       <c r="N126" s="94"/>
     </row>
     <row r="127" spans="1:14" ht="42.3" x14ac:dyDescent="0.5">
-      <c r="A127" s="192"/>
+      <c r="A127" s="198"/>
       <c r="B127" s="83" t="s">
         <v>654</v>
       </c>
@@ -17775,7 +17775,7 @@
       <c r="F127" s="94"/>
     </row>
     <row r="128" spans="1:14" ht="42.3" x14ac:dyDescent="0.5">
-      <c r="A128" s="192"/>
+      <c r="A128" s="198"/>
       <c r="B128" s="83" t="s">
         <v>655</v>
       </c>
@@ -17788,7 +17788,7 @@
       <c r="F128" s="94"/>
     </row>
     <row r="129" spans="1:14" ht="42.3" x14ac:dyDescent="0.5">
-      <c r="A129" s="193"/>
+      <c r="A129" s="199"/>
       <c r="B129" s="83" t="s">
         <v>656</v>
       </c>
@@ -17824,6 +17824,50 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A115:D115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:A4"/>
@@ -17836,50 +17880,6 @@
     <mergeCell ref="A45:A49"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A53:A56"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A104:B104"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A116:B116"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18119,25 +18119,25 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="210" t="s">
+      <c r="A5" s="219" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="210"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="210"/>
-      <c r="H5" s="210"/>
-      <c r="I5" s="210"/>
-      <c r="J5" s="210"/>
-      <c r="K5" s="210"/>
-      <c r="L5" s="210"/>
-      <c r="M5" s="210"/>
-      <c r="N5" s="210"/>
-      <c r="O5" s="210"/>
-      <c r="P5" s="210"/>
-      <c r="Q5" s="210"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="219"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="219"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
+      <c r="M5" s="219"/>
+      <c r="N5" s="219"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="219"/>
       <c r="R5" s="8">
         <f>(R2/R4)*100</f>
         <v>79.891304347826093</v>
@@ -18168,13 +18168,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="169" t="s">
         <v>707</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="130" t="s">
@@ -18226,11 +18226,11 @@
       <c r="E4" s="69" t="s">
         <v>716</v>
       </c>
-      <c r="G4" s="212" t="s">
+      <c r="G4" s="170" t="s">
         <v>1052</v>
       </c>
-      <c r="H4" s="212"/>
-      <c r="I4" s="212"/>
+      <c r="H4" s="170"/>
+      <c r="I4" s="170"/>
     </row>
     <row r="5" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="131" t="s">
@@ -18248,9 +18248,9 @@
       <c r="E5" s="69" t="s">
         <v>718</v>
       </c>
-      <c r="G5" s="212"/>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
     </row>
     <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="131" t="s">
@@ -18311,20 +18311,20 @@
       <c r="E9" s="71"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="215" t="s">
+      <c r="A10" s="227" t="s">
         <v>804</v>
       </c>
-      <c r="B10" s="215"/>
-      <c r="C10" s="215"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
+      <c r="B10" s="227"/>
+      <c r="C10" s="227"/>
+      <c r="D10" s="227"/>
+      <c r="E10" s="227"/>
+      <c r="F10" s="227"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="214" t="s">
+      <c r="A11" s="226" t="s">
         <v>805</v>
       </c>
-      <c r="B11" s="214"/>
+      <c r="B11" s="226"/>
       <c r="C11" s="132" t="s">
         <v>726</v>
       </c>
@@ -18339,10 +18339,10 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="211" t="s">
+      <c r="A12" s="223" t="s">
         <v>729</v>
       </c>
-      <c r="B12" s="211"/>
+      <c r="B12" s="223"/>
       <c r="C12" s="74" t="s">
         <v>730</v>
       </c>
@@ -18357,10 +18357,10 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="211" t="s">
+      <c r="A13" s="223" t="s">
         <v>498</v>
       </c>
-      <c r="B13" s="211"/>
+      <c r="B13" s="223"/>
       <c r="C13" s="74" t="s">
         <v>732</v>
       </c>
@@ -18375,10 +18375,10 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="211" t="s">
+      <c r="A14" s="223" t="s">
         <v>734</v>
       </c>
-      <c r="B14" s="211"/>
+      <c r="B14" s="223"/>
       <c r="C14" s="74" t="s">
         <v>735</v>
       </c>
@@ -18393,10 +18393,10 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="211" t="s">
+      <c r="A15" s="223" t="s">
         <v>736</v>
       </c>
-      <c r="B15" s="211"/>
+      <c r="B15" s="223"/>
       <c r="C15" s="74" t="s">
         <v>737</v>
       </c>
@@ -18411,10 +18411,10 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="211" t="s">
+      <c r="A16" s="223" t="s">
         <v>739</v>
       </c>
-      <c r="B16" s="211"/>
+      <c r="B16" s="223"/>
       <c r="C16" s="74" t="s">
         <v>405</v>
       </c>
@@ -18429,10 +18429,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="211" t="s">
+      <c r="A17" s="223" t="s">
         <v>741</v>
       </c>
-      <c r="B17" s="211"/>
+      <c r="B17" s="223"/>
       <c r="C17" s="74" t="s">
         <v>417</v>
       </c>
@@ -18447,10 +18447,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="211" t="s">
+      <c r="A18" s="223" t="s">
         <v>743</v>
       </c>
-      <c r="B18" s="211"/>
+      <c r="B18" s="223"/>
       <c r="C18" s="74" t="s">
         <v>737</v>
       </c>
@@ -18465,10 +18465,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="211" t="s">
+      <c r="A19" s="223" t="s">
         <v>745</v>
       </c>
-      <c r="B19" s="211"/>
+      <c r="B19" s="223"/>
       <c r="C19" s="72" t="s">
         <v>803</v>
       </c>
@@ -18483,10 +18483,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="211" t="s">
+      <c r="A20" s="223" t="s">
         <v>747</v>
       </c>
-      <c r="B20" s="211"/>
+      <c r="B20" s="223"/>
       <c r="C20" s="72" t="s">
         <v>762</v>
       </c>
@@ -18501,10 +18501,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="211" t="s">
+      <c r="A21" s="223" t="s">
         <v>749</v>
       </c>
-      <c r="B21" s="211"/>
+      <c r="B21" s="223"/>
       <c r="C21" s="72" t="s">
         <v>762</v>
       </c>
@@ -18519,10 +18519,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="223" t="s">
+      <c r="A22" s="224" t="s">
         <v>935</v>
       </c>
-      <c r="B22" s="224"/>
+      <c r="B22" s="225"/>
       <c r="C22" s="72" t="s">
         <v>1073</v>
       </c>
@@ -18537,10 +18537,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="223" t="s">
+      <c r="A23" s="224" t="s">
         <v>938</v>
       </c>
-      <c r="B23" s="224"/>
+      <c r="B23" s="225"/>
       <c r="C23" s="72" t="s">
         <v>762</v>
       </c>
@@ -18555,10 +18555,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="223" t="s">
+      <c r="A24" s="224" t="s">
         <v>940</v>
       </c>
-      <c r="B24" s="224"/>
+      <c r="B24" s="225"/>
       <c r="C24" s="72" t="s">
         <v>762</v>
       </c>
@@ -18573,10 +18573,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="223" t="s">
+      <c r="A25" s="224" t="s">
         <v>944</v>
       </c>
-      <c r="B25" s="224"/>
+      <c r="B25" s="225"/>
       <c r="C25" s="72" t="s">
         <v>762</v>
       </c>
@@ -18591,13 +18591,13 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="225" t="s">
+      <c r="A27" s="220" t="s">
         <v>751</v>
       </c>
-      <c r="B27" s="226"/>
-      <c r="C27" s="226"/>
-      <c r="D27" s="226"/>
-      <c r="E27" s="227"/>
+      <c r="B27" s="221"/>
+      <c r="C27" s="221"/>
+      <c r="D27" s="221"/>
+      <c r="E27" s="222"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="130" t="s">
@@ -18702,14 +18702,14 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="143" t="s">
+      <c r="A35" s="147" t="s">
         <v>763</v>
       </c>
-      <c r="B35" s="144"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="145"/>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="149"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="130" t="s">
@@ -19380,11 +19380,11 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="169" t="s">
         <v>340</v>
       </c>
-      <c r="B71" s="213"/>
-      <c r="C71" s="213"/>
+      <c r="B71" s="169"/>
+      <c r="C71" s="169"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="130" t="s">
@@ -19465,15 +19465,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G4:I5"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A11:B11"/>
@@ -19486,6 +19477,15 @@
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="G4:I5"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
